--- a/output/云端_2026-10-25_千问调试集53篇/S39_机制句复核/S39_机制句复核.xlsx
+++ b/output/云端_2026-10-25_千问调试集53篇/S39_机制句复核/S39_机制句复核.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐句复核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题汇总（要你定）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题汇总" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -446,98 +446,119 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI 辅助复核，用户尚未逐项人工确认。判定是 Claude 按规程 §5.7 逐句读原文给的建议，口径待定的几类要用户定。</t>
+          <t>AI 辅助复核，用户尚未逐项人工确认。判定是 Claude 逐句读原文给的，口径按 10-25 用户定的 5 条（方案 §5.7“哪些句子算机制原句”）。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>范围：五家挂在“机制”里的全部原句（并集 85 句）+ 五家都没挂、但应记的 9 句，共 94 句。只判“这句该不该作为机制原句”和“来源标注对不对”，不判机制概括、过程大类、强/弱侧写得对不对。</t>
+          <t>注意：五家都是按旧规程（没有这 5 条）提的，所以“重复”“应放性质”“引言背景”这几类挂了也不全是它们的错；要公平比，得按新规程重跑。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>只有 S39 一篇，是 Claude 提得最多的一篇，不能代表 53 篇。</t>
+          <t>范围：五家挂在“机制”里的全部原句（并集 85 句）+ 五家都没挂、但应记的 10 句，共 95 句。只判“这句该不该作为机制原句”和“来源标注对不对”，不判机制概括、过程大类、强/弱侧写得对不对。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>判定代码：</t>
+          <t>只有 S39 一篇，是 Claude 提得最多的一篇，不能代表 53 篇。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A：应记：本文机制说法（含排除性说法，如“电导率不是原因”）</t>
+          <t>判定代码：</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  B：应记：本文推测（may / likely 等）</t>
+          <t xml:space="preserve">  A：应记：本文机制说法（含排除性说法，如“电导率不是原因”）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  续接：被切断的半句，与下一句同属一句；挂上不算错，不计数</t>
+          <t xml:space="preserve">  B：应记：本文推测（may / likely 等）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  C：口径待定：引言/背景转述、通用规律（带引文）</t>
+          <t xml:space="preserve">  T：应记：正文/SI 里引用别人结论支撑本文解释的句子，标“转述”</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  E：口径待定：只讲性质本身或性质来源（分子结构 → 溶剂化/溶解度），不涉及四类过程</t>
+          <t xml:space="preserve">  续接：被切断的半句，与下一句同属一句；挂上不算错，不计数</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  D：不该记：纯数据、表征观察、方法、小标题、计算</t>
+          <t xml:space="preserve">  R：不记：摘要、引言末预告、结论里与正文重复的说法（正文有对应句）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>格子里的符号：✅ 应记且挂了；❌漏 应记没挂；❌错提 挂了不该记的句子；🔶 挂了口径待定的句子；⚠️ 来源标注与判定不符（M0097、M0115 半句转述半句本文结论，不判来源）。符号后是该家的机制编号。</t>
+          <t xml:space="preserve">  P：不进机制：只讲性质本身或性质来源（分子结构 → 溶剂化/溶解度），应记在“性质”下</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>代码核对：94 个句子编号全部在 S39 原文里找到（✅）；五家挂的句子都已判定（脚本断言）。</t>
+          <t xml:space="preserve">  I：不记：引言背景</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>千问 Max 这一版格式 3 轮都没过（多一个括号），程序删掉括号后另存，仅供对比，未冻结。</t>
+          <t xml:space="preserve">  D：不记：纯数据、表征观察、方法、小标题、计算</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>“挂的句子里应记的比例”= 应记句命中 ÷（挂的原句 − 续接半句）；口径待定的句子按“不算应记”计，用户定口径后会变。</t>
+          <t>格子里的符号：✅ 应记且挂了；❌漏 应记没挂；❌错提 挂了引言背景或数据/方法句；🔶重复 挂了摘要/预告/结论里的重复说法；🔶应放性质 把性质来源放进了机制；⚠️ 来源标注与判定不符（M0097、M0115 半句转述半句本文结论，不判来源）。符号后是该家的机制编号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>代码核对：95 个句子编号全部在 S39 原文里找到（✅）；五家挂的句子都已判定（脚本断言）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>千问 Max 这一版格式 3 轮都没过（多一个括号），程序删掉括号后另存，仅供对比，未冻结。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>“挂的句子里应记的比例”= 应记句命中 ÷（挂的原句 − 续接半句）。</t>
         </is>
       </c>
     </row>
@@ -552,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -646,19 +667,19 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>16</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -668,19 +689,19 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
@@ -690,126 +711,126 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.667</v>
+        <v>0.768</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.242</v>
+        <v>0.286</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.47</v>
+        <v>0.411</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.47</v>
+        <v>0.482</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.227</v>
+        <v>0.196</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>应记句命中（不计摘要/预告/结论）</t>
+          <t>挂的句子里应记的比例</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>42</v>
+        <v>0.796</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>23</v>
+        <v>0.676</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>26</v>
+        <v>0.587</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>11</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>应记句总数（不计摘要/预告/结论）</t>
+          <t>错提（引言背景、数据、方法）</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>应记句召回（不计摘要/预告/结论）</t>
+          <t>性质来源放进机制</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.792</v>
+        <v>1</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.302</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.434</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.491</v>
+        <v>8</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>挂的句子里应记的比例</t>
+          <t>重复说法（摘要/预告/结论）</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>2</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.912</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.674</v>
+        <v>5</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9379999999999999</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>口径待定句（C/E）</t>
+          <t>来源标注不符</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
@@ -818,162 +839,118 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>错提（D）</t>
+          <t>来源可判句数</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>来源标注不符</t>
+          <t>配方</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>来源可判句数</t>
+          <t>测试</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>配方</t>
+          <t>结果</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>测试</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>结果</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Claude 子代理，对话内提取</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>GPT 子代理，对话内提取</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>格式 3 轮未过；程序删一个多余括号后仅供对比，未冻结</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -990,7 +967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1086,39 +1063,27 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>摘要里作者的结论：Li⁺ 溶解度/溶剂化 → 电导率、锂负极可逆性</t>
+          <t>摘要里作者的结论：Li⁺ 溶解度/溶剂化 → 电导率、锂负极可逆性；正文对应句 M0069/M0070、S0156</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M1</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>🔶重复 S39-M1</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M1</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>🔶重复 S39-M1</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1143,39 +1108,27 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>摘要里作者的结论：LiPS 溶剂化管热力学、溶解度管动力学</t>
+          <t>摘要里作者的结论：LiPS 溶剂化管热力学、溶解度管动力学；正文对应句 M0101、M0136</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M2</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>🔶重复 S39-M2</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M2</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>🔶重复 S39-M2</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1200,39 +1153,23 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>摘要：F4DEE 低 LiPS 溶解度 + 中等 Li⁺ 溶剂化 → 负极稳定、正极动力学够用、寿命长</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>❌漏（挂在设计主张）</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>摘要：F4DEE 低 LiPS 溶解度 + 中等 Li⁺ 溶剂化 → 负极稳定、正极动力学够用、寿命长；正文对应句 M0158</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M3</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>❌漏（挂在设计主张）</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>❌漏（挂在设计主张）</t>
-        </is>
-      </c>
+          <t>🔶重复 S39-M3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1257,7 +1194,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1267,7 +1204,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>🔶 S39-M3</t>
+          <t>❌错提 S39-M3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1298,7 +1235,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1308,13 +1245,13 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>🔶 S39-M3</t>
+          <t>❌错提 S39-M3</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>🔶 S39-M4</t>
+          <t>❌错提 S39-M4</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -1343,7 +1280,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1353,7 +1290,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>🔶 S39-M4</t>
+          <t>❌错提 S39-M4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -1384,7 +1321,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1394,7 +1331,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>🔶 S39-M4</t>
+          <t>❌错提 S39-M4</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -1425,39 +1362,23 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>作者预告本文结论：电导率都高、与 Li⁺ 溶剂化强弱无关（排除性说法）</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>作者预告本文结论：电导率都高、与 Li⁺ 溶剂化强弱无关（排除性说法）；正文对应句 S0119</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M8</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>🔶重复 S39-M8</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1482,39 +1403,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>预告：中等 Li⁺ 溶剂化 → 调控沉积/剥离 → 负极稳定</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>预告：中等 Li⁺ 溶剂化 → 调控沉积/剥离 → 负极稳定；正文对应句 M0072</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M5</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>🔶重复 S39-M5</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1539,37 +1444,29 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>预告：弱 LiPS 溶剂化 → 偏向短链、促进氧化</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>预告：弱 LiPS 溶剂化 → 偏向短链、促进氧化；正文对应句 M0096、M0109、M0111</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M6</t>
+          <t>🔶重复 S39-M6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M3</t>
+          <t>🔶重复 S39-M3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M2</t>
+          <t>🔶重复 S39-M2</t>
         </is>
       </c>
     </row>
@@ -1596,37 +1493,29 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>预告：→ 正极可逆性提高、保护负极免受长链 LiPS 腐蚀</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>预告：→ 正极可逆性提高、保护负极免受长链 LiPS 腐蚀；正文对应句 M0118</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M6</t>
+          <t>🔶重复 S39-M6</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M2</t>
+          <t>🔶重复 S39-M2</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M2</t>
+          <t>🔶重复 S39-M2</t>
         </is>
       </c>
     </row>
@@ -1653,37 +1542,29 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>预告：过电位小与 LiPS 溶解度高相关（扩散）</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>预告：过电位小与 LiPS 溶解度高相关（扩散）；正文对应句 M0122、M0136</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M7</t>
+          <t>🔶重复 S39-M7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M4</t>
+          <t>🔶重复 S39-M4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M3</t>
+          <t>🔶重复 S39-M3</t>
         </is>
       </c>
     </row>
@@ -1710,37 +1591,29 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>预告：中等溶解度 → 动力学快 → 过电位低</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>预告：中等溶解度 → 动力学快 → 过电位低；正文对应句 M0136</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M7</t>
+          <t>🔶重复 S39-M7</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M4</t>
+          <t>🔶重复 S39-M4</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M3</t>
+          <t>🔶重复 S39-M3</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1640,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1780,7 +1653,7 @@
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>🔶 S39-M7</t>
+          <t>🔶应放性质 S39-M7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
@@ -1808,7 +1681,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1821,7 +1694,7 @@
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>🔶 S39-M7</t>
+          <t>🔶应放性质 S39-M7</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -1849,7 +1722,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1862,7 +1735,7 @@
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>🔶 S39-M7</t>
+          <t>🔶应放性质 S39-M7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
@@ -1890,23 +1763,39 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>讲盐浓度的通用规律（引文 4、30、31），用来定 1.0 M，不是本文溶剂梯度的结论</t>
+          <t>讲盐浓度的通用规律（引文 4、30、31），用来定 1.0 M，不是本文溶剂梯度的结论；不在引言，按 10-25 口径照记、标转述</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>🔶 S39-M46</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
+          <t>✅ S39-M46</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4518,39 +4407,19 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>结论：中等 Li⁺ 溶剂化 → 富氟 SEI → 调控沉积/剥离</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>结论：中等 Li⁺ 溶剂化 → 富氟 SEI → 调控沉积/剥离；正文对应句 M0072、M0077</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4575,39 +4444,19 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>结论：弱 LiPS 溶剂化 → 抑制长链 LiPS → 负极稳定、正极可逆</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>结论：弱 LiPS 溶剂化 → 抑制长链 LiPS → 负极稳定、正极可逆；正文对应句 M0118</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4632,39 +4481,19 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>结论：中等 LiPS 溶解度 → 浓差极化小 → 动力学好</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>结论：中等 LiPS 溶解度 → 浓差极化小 → 动力学好；正文对应句 M0136</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4689,39 +4518,19 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>结论：以上 → 寿命延长</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>结论：以上 → 寿命延长；正文对应句 M0158、M0159</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4746,7 +4555,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -4759,7 +4568,7 @@
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>🔶 S39-M7</t>
+          <t>🔶应放性质 S39-M7</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
@@ -4787,7 +4596,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -4800,7 +4609,7 @@
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>🔶 S39-M7</t>
+          <t>🔶应放性质 S39-M7</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
@@ -4828,7 +4637,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -4841,7 +4650,7 @@
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>🔶 S39-M7</t>
+          <t>🔶应放性质 S39-M7</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
@@ -4869,7 +4678,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -4882,7 +4691,7 @@
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>🔶 S39-M7</t>
+          <t>🔶应放性质 S39-M7</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
@@ -4910,7 +4719,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -4923,7 +4732,7 @@
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>🔶 S39-M7</t>
+          <t>🔶应放性质 S39-M7</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
@@ -5437,7 +5246,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>S0165</t>
+          <t>S0164</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -5452,17 +5261,17 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Therefore, the LiF-rich SEI layer formed by the DOL/F4DEE electrolyte effectively suppresses Li dendrite growth, leading to enhanced Li cyclability.7, 9 Figure S17.</t>
+          <t>LiF is well known to regulate Li deposition because of its electrochemical stability and mechanical strength.</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>富 LiF SEI → 抑制枝晶 → 锂循环好（引文 7、9，与他文一致）</t>
+          <t>“LiF is well known to regulate Li deposition”：SI 里的通用说法，支撑本文 SEI 解释，照记、标转述</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -5494,48 +5303,64 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>S0169</t>
+          <t>S0165</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SI p21</t>
+          <t>SI p20</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>SI Note S4</t>
+          <t>SI Note S3</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>SI-20 Note S4 Suppressed lithium anode chemical corrosion with weak LiPS solvation LiPS in Li-S batteries, especially long-chain species (x = 5 ~ 8 in Li2Sx), can chemically corrode Li anode, causing irreversible Li inventory loss.10, 11 Here we quantified the effect of LiPS solvation on this parasitic reaction via titration gas chromatography (TGC).</t>
+          <t>Therefore, the LiF-rich SEI layer formed by the DOL/F4DEE electrolyte effectively suppresses Li dendrite growth, leading to enhanced Li cyclability.7, 9 Figure S17.</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Note S4 标题 + 背景（长链 LiPS 腐蚀锂，引文 10、11）+ 方法</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr"/>
+          <t>富 LiF SEI → 抑制枝晶 → 锂循环好（引文 7、9，与他文一致）</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>🔶⚠️标“本文结论” S39-M10</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr"/>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>S0170</t>
+          <t>S0169</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -5550,33 +5375,49 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Li metal chips were soaked in 1.0 mL LiPS solutions (0.1 M Li2S6 dissolved in DOL/DME, DOL/F4DEE or DOL/TTE) for 25 days.</t>
+          <t>SI-20 Note S4 Suppressed lithium anode chemical corrosion with weak LiPS solvation LiPS in Li-S batteries, especially long-chain species (x = 5 ~ 8 in Li2Sx), can chemically corrode Li anode, causing irreversible Li inventory loss.10, 11 Here we quantified the effect of LiPS solvation on this parasitic reaction via titration gas chromatography (TGC).</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>实验步骤</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr"/>
-      <c r="I87" s="2" t="inlineStr"/>
+          <t>Note S4 标题 + 背景（长链 LiPS 腐蚀锂，引文 10、11）+ 方法；不在引言，按 10-25 口径照记、标转述</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>❌错提 S39-M10</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr"/>
+          <t>✅⚠️标“本文结论” S39-M10</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>S0177</t>
+          <t>S0170</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5591,49 +5432,33 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>S2) Per Figure S18b, LiPS solutions with weaker LiPS solvation result in lower Li inventory loss ratio.</t>
+          <t>Li metal chips were soaked in 1.0 mL LiPS solutions (0.1 M Li2S6 dissolved in DOL/DME, DOL/F4DEE or DOL/TTE) for 25 days.</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>LiPS 溶剂化越弱，锂库存损失越少</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>✅ S39-M12</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>✅ S39-M20</t>
-        </is>
-      </c>
+          <t>实验步骤</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M10</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>❌错提 S39-M10</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>S0178</t>
+          <t>S0177</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5648,7 +5473,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>This proves that weak LiPS solvation can suppress chemical corrosion on Li anode despite its relatively small benefit.</t>
+          <t>S2) Per Figure S18b, LiPS solutions with weaker LiPS solvation result in lower Li inventory loss ratio.</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -5658,7 +5483,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>接上句：弱 LiPS 溶剂化能抑制锂腐蚀（作者说益处较小）</t>
+          <t>LiPS 溶剂化越弱，锂库存损失越少</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -5668,7 +5493,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M14</t>
+          <t>❌漏</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -5690,22 +5515,22 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>S0212</t>
+          <t>S0178</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>SI p23</t>
+          <t>SI p21</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>SI Note S5</t>
+          <t>SI Note S4</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>The overpotential on each stage does not significantly change with varied LiPS solvation, again evidencing the non-correlation between LiPS solvation and LiPS reduction kinetics.</t>
+          <t>This proves that weak LiPS solvation can suppress chemical corrosion on Li anode despite its relatively small benefit.</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5715,27 +5540,27 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>各段过电位不随 LiPS 溶剂化变 → 溶剂化与还原动力学无关（排除性）</t>
+          <t>接上句：弱 LiPS 溶剂化能抑制锂腐蚀（作者说益处较小）</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M12</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M14</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M20</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M10</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -5747,7 +5572,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>S0213</t>
+          <t>S0212</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -5762,7 +5587,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>(3) The discharge capacity on stage II maintains the same order of DOL/DME &gt; DOL/F4DEE &gt; DOL/TTE, demonstrating the favored liquid-liquid LiPS reduction with strong LiPS solvation.</t>
+          <t>The overpotential on each stage does not significantly change with varied LiPS solvation, again evidencing the non-correlation between LiPS solvation and LiPS reduction kinetics.</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -5772,12 +5597,12 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>第 II 段容量顺序 → 强 LiPS 溶剂化利于液–液还原</t>
+          <t>各段过电位不随 LiPS 溶剂化变 → 溶剂化与还原动力学无关（排除性）</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M47</t>
+          <t>❌漏</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5804,48 +5629,64 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>S0225</t>
+          <t>S0213</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>SI p26</t>
+          <t>SI p23</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SI Note S5</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>S5 and completely dissolves in the electrolyte, the maximum Li2S6 concentration is 0.52 M. 3 S8 (s) + 8 Li+ + 8 e- → 4 Li2S6 (sol) (Eq.</t>
+          <t>(3) The discharge capacity on stage II maintains the same order of DOL/DME &gt; DOL/F4DEE &gt; DOL/TTE, demonstrating the favored liquid-liquid LiPS reduction with strong LiPS solvation.</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>计算 Li₂S₆ 最大浓度</t>
+          <t>第 II 段容量顺序 → 强 LiPS 溶剂化利于液–液还原</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>❌错提 S39-M45</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-      <c r="K92" s="2" t="inlineStr"/>
+          <t>✅ S39-M47</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>S0226</t>
+          <t>S0225</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -5860,7 +5701,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>S5) This value is lower than Li2S6 solubility in DOL/DME but exceeds that in DOL/F4DEE and DOL/TTE.</t>
+          <t>S5 and completely dissolves in the electrolyte, the maximum Li2S6 concentration is 0.52 M. 3 S8 (s) + 8 Li+ + 8 e- → 4 Li2S6 (sol) (Eq.</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5870,7 +5711,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>数值比较（接 S0225）</t>
+          <t>计算 Li₂S₆ 最大浓度</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -5886,7 +5727,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>S0227</t>
+          <t>S0226</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -5901,22 +5742,22 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>This indicates that the moderate LiPS solubility in DOL/F4DEE electrolyte limits the soluble LiPS concentration.</t>
+          <t>S5) This value is lower than Li2S6 solubility in DOL/DME but exceeds that in DOL/F4DEE and DOL/TTE.</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>只讲性质本身：中等溶解度限制可溶 LiPS 浓度，没有落到过程</t>
+          <t>数值比较（接 S0225）</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>🔶 S39-M45</t>
+          <t>❌错提 S39-M45</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
@@ -5927,55 +5768,96 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>S0227</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>SI p26</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>This indicates that the moderate LiPS solubility in DOL/F4DEE electrolyte limits the soluble LiPS concentration.</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>只讲性质本身：中等溶解度限制可溶 LiPS 浓度，没有落到过程</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>🔶应放性质 S39-M45</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
           <t>S0265</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>SI p37</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>SI 图注</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Li-S cell with DOL/TTE experiences a slow capacity activation and overpotential recovery process, demonstrating the negative effects of its poor LiPS solubility.</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>TTE 容量活化慢、过电位恢复慢 → 溶解度低的负面作用</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>✅ S39-M12</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
         <is>
           <t>✅ S39-M6</t>
         </is>
       </c>
-      <c r="K95" s="2" t="inlineStr">
+      <c r="K96" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
         </is>
@@ -6025,51 +5907,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>建议（AI 辅助，待用户定）</t>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>口径</t>
+          <t>已定口径</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>引言/背景转述（C）要不要记</t>
+          <t>引言背景不记；正文转述照记标“转述”</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>规程说“只靠转述句支撑的说法照记、标转述”，但没说引言背景是否要穷尽。五家做法不一：Claude 记了 6 句、千问 Max 记 1 句、其他 0 句</t>
+          <t>10-25 用户定</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>M0010、M0011、M0015、M0067、S0169</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>建议：引言背景不记；正文里作者拿别人的结论支撑自己解释的句子照记、标转述</t>
-        </is>
-      </c>
+          <t>I：M0010、M0011、M0014、M0015；T：M0067、S0164、S0169</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>口径</t>
+          <t>已定口径</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>性质来源句（E）要不要记</t>
+          <t>性质来源放进“性质”，不进机制</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>分子结构 → 溶剂化/溶解度的解释，不涉及四类过程。千问 27B 开思考挂了 9 句，其他家 0–1 句</t>
+          <t>10-25 用户定</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -6079,51 +5957,47 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>建议：不进“机制”；有需要时放进“性质”的 method/备注</t>
+          <t>新版提示词 properties 加 origin 字段</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>口径</t>
+          <t>已定口径</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>摘要、引言末预告、结论里重复的说法要不要每句都记</t>
+          <t>摘要/引言末预告/结论里的重复说法只记正文那句</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>同一说法在摘要、引言末、正文、结论各说一遍。千问三种设置都挂了引言末预告（M0023–M0026），Claude 挂了摘要，五家都没挂结论 M0167–M0170</t>
+          <t>10-25 用户定；S39 这 13 句正文都有对应句</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>M0003–M0005、M0021–M0026、M0158、M0167–M0170</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>建议：同一说法只记正文那一句；正文没有的才用摘要/结论句</t>
-        </is>
-      </c>
+          <t>M0003–M0005、M0021–M0026、M0167–M0170</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>口径</t>
+          <t>已定口径</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>排除性说法（“电导率不是原因”“界面动力学可忽略”）算不算</t>
+          <t>排除性说法算机制</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>规程允许“只讲电导率时过程大类为空”，本表按应记算。五家都漏得多</t>
+          <t>10-25 用户定</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -6131,26 +6005,22 @@
           <t>M0021、M0088、M0100、S0119、S0120、S0154、S0156、S0162、S0212</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>建议：算，是判断两侧短板的关键证据</t>
-        </is>
-      </c>
+      <c r="E5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>口径</t>
+          <t>已定口径</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>一句一条还是多句一条</t>
+          <t>一句一条；被切断可挂连续 2 句</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>规程“一句整句原文一条”。千问 27B 开思考把 46 句塞进 11 条，GPT 一句一条但只挂 16 句，Claude 47 条挂 55 句</t>
+          <t>10-25 用户定；千问 27B 开思考把 46 句塞进 11 条</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -6158,11 +6028,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>建议：保留一句一条；同一说法跨两句时可挂连续 2 句</t>
-        </is>
-      </c>
+      <c r="E6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -6182,12 +6048,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>M0087、M0137、M0167、M0168、M0169、M0170、S0120、S0165、S0212</t>
+          <t>M0087、M0137、S0120、S0164、S0165、S0212</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>说明召回率是按这 94 句算的，原文里可能还有五家和本表都漏的</t>
+          <t>召回率按本表的句子算，原文里可能还有五家和本表都漏的</t>
         </is>
       </c>
     </row>
@@ -6204,12 +6070,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>纯数据/方法/小标题/计算</t>
+          <t>引言背景、纯数据/方法/小标题/计算</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>M0110、M0142、S0225、S0226</t>
+          <t>M0010、M0011、M0014、M0015、M0110、M0142、S0225、S0226</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -6227,12 +6093,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>纯数据/方法/小标题/计算</t>
+          <t>引言背景、纯数据/方法/小标题/计算</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>M0071、M0126</t>
+          <t>M0011、M0071、M0126</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -6250,7 +6116,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>纯数据/方法/小标题/计算</t>
+          <t>引言背景、纯数据/方法/小标题/计算</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -6292,7 +6158,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>纯数据/方法/小标题/计算</t>
+          <t>引言背景、纯数据/方法/小标题/计算</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">

--- a/output/云端_2026-10-25_千问调试集53篇/S39_机制句复核/S39_机制句复核.xlsx
+++ b/output/云端_2026-10-25_千问调试集53篇/S39_机制句复核/S39_机制句复核.xlsx
@@ -460,7 +460,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>范围：五家挂在“机制”里的全部原句（并集 85 句）+ 五家都没挂、但应记的 10 句，共 95 句。只判“这句该不该作为机制原句”和“来源标注对不对”，不判机制概括、过程大类、强/弱侧写得对不对。</t>
+          <t>范围：各家挂在“机制”里的全部原句 + 都没挂、但应记的句子，共 97 句。只判“这句该不该作为机制原句”和“来源标注对不对”，不判机制概括、过程大类、强/弱侧写得对不对。</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>代码核对：95 个句子编号全部在 S39 原文里找到（✅）；五家挂的句子都已判定（脚本断言）。</t>
+          <t>代码核对：97 个句子编号全部在 S39 原文里找到（✅）；五家挂的句子都已判定（脚本断言）。</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -582,6 +582,7 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -615,6 +616,11 @@
           <t>千问27B关思考</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>智谱GLM-5.3关思考</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -637,6 +643,9 @@
       <c r="F2" s="2" t="n">
         <v>4</v>
       </c>
+      <c r="G2" s="2" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -659,6 +668,9 @@
       <c r="F3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="G3" s="2" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -681,6 +693,9 @@
       <c r="F4" s="2" t="n">
         <v>11</v>
       </c>
+      <c r="G4" s="2" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -703,6 +718,9 @@
       <c r="F5" s="2" t="n">
         <v>56</v>
       </c>
+      <c r="G5" s="2" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -725,6 +743,9 @@
       <c r="F6" s="2" t="n">
         <v>0.196</v>
       </c>
+      <c r="G6" s="2" t="n">
+        <v>0.393</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -747,6 +768,9 @@
       <c r="F7" s="2" t="n">
         <v>0.6879999999999999</v>
       </c>
+      <c r="G7" s="2" t="n">
+        <v>0.786</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -769,6 +793,9 @@
       <c r="F8" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="G8" s="2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -791,6 +818,9 @@
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G9" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -813,6 +843,9 @@
       <c r="F10" s="2" t="n">
         <v>4</v>
       </c>
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -835,6 +868,9 @@
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -857,6 +893,9 @@
       <c r="F12" s="2" t="n">
         <v>10</v>
       </c>
+      <c r="G12" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -879,6 +918,9 @@
       <c r="F13" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="G13" s="2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -901,6 +943,9 @@
       <c r="F14" s="2" t="n">
         <v>4</v>
       </c>
+      <c r="G14" s="2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -923,6 +968,9 @@
       <c r="F15" s="2" t="n">
         <v>9</v>
       </c>
+      <c r="G15" s="2" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -953,6 +1001,11 @@
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>API</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>API；用新版提示词 v2（含 10-25 机制句口径），其余各家用旧版</t>
         </is>
       </c>
     </row>
@@ -967,7 +1020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -981,6 +1034,7 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,6 +1093,11 @@
           <t>千问27B关思考</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>智谱GLM-5.3关思考</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1084,6 +1143,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1129,6 +1189,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1170,6 +1231,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1211,6 +1273,7 @@
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1256,6 +1319,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1297,6 +1361,7 @@
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1338,6 +1403,7 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1379,6 +1445,7 @@
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1420,6 +1487,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1469,6 +1537,7 @@
           <t>🔶重复 S39-M2</t>
         </is>
       </c>
+      <c r="L11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1518,6 +1587,7 @@
           <t>🔶重复 S39-M2</t>
         </is>
       </c>
+      <c r="L12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1567,6 +1637,7 @@
           <t>🔶重复 S39-M3</t>
         </is>
       </c>
+      <c r="L13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1616,6 +1687,7 @@
           <t>🔶重复 S39-M3</t>
         </is>
       </c>
+      <c r="L14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1657,6 +1729,7 @@
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1698,6 +1771,7 @@
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1739,6 +1813,7 @@
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1796,6 +1871,11 @@
           <t>❌漏</t>
         </is>
       </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1853,6 +1933,11 @@
           <t>✅ S39-M1</t>
         </is>
       </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1908,6 +1993,11 @@
       <c r="K20" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M1</t>
         </is>
       </c>
     </row>
@@ -1951,6 +2041,11 @@
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>❌错提 S39-M1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2008,6 +2103,11 @@
           <t>✅ S39-M1</t>
         </is>
       </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M2</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2063,6 +2163,11 @@
       <c r="K23" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M2</t>
         </is>
       </c>
     </row>
@@ -2106,6 +2211,7 @@
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2163,6 +2269,11 @@
           <t>✅ S39-M1</t>
         </is>
       </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M3</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2220,6 +2331,11 @@
           <t>✅ S39-M1</t>
         </is>
       </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M3</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2277,6 +2393,11 @@
           <t>✅ S39-M2</t>
         </is>
       </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2334,6 +2455,11 @@
           <t>❌漏</t>
         </is>
       </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2391,6 +2517,11 @@
           <t>❌漏</t>
         </is>
       </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2448,6 +2579,11 @@
           <t>❌漏</t>
         </is>
       </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M8</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2505,6 +2641,11 @@
           <t>❌漏</t>
         </is>
       </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M8</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2562,6 +2703,11 @@
           <t>❌漏</t>
         </is>
       </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2617,6 +2763,11 @@
       <c r="K33" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M9</t>
         </is>
       </c>
     </row>
@@ -2660,6 +2811,7 @@
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2717,6 +2869,11 @@
           <t>❌漏</t>
         </is>
       </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2770,6 +2927,11 @@
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
         </is>
@@ -2815,6 +2977,7 @@
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2872,6 +3035,11 @@
           <t>❌漏</t>
         </is>
       </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2929,6 +3097,11 @@
           <t>❌漏</t>
         </is>
       </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M10</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2986,6 +3159,11 @@
           <t>❌漏</t>
         </is>
       </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3043,6 +3221,11 @@
           <t>❌漏</t>
         </is>
       </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3100,6 +3283,11 @@
           <t>✅ S39-M2</t>
         </is>
       </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M10</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3157,6 +3345,11 @@
           <t>❌漏</t>
         </is>
       </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3214,6 +3407,11 @@
           <t>❌漏</t>
         </is>
       </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3271,6 +3469,11 @@
           <t>✅ S39-M2</t>
         </is>
       </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3328,6 +3531,11 @@
           <t>❌漏</t>
         </is>
       </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3385,6 +3593,11 @@
           <t>❌漏</t>
         </is>
       </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3440,6 +3653,11 @@
       <c r="K48" s="2" t="inlineStr">
         <is>
           <t>✅ S39-M3</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
         </is>
       </c>
     </row>
@@ -3487,16 +3705,17 @@
           <t>❌错提 S39-M3</t>
         </is>
       </c>
+      <c r="L49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>M0136</t>
+          <t>M0127</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>正文 p7</t>
+          <t>正文 p6</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3506,49 +3725,34 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>These results highlight the critical role of LiPS solubility in governing Li−S redox kinetics: higher LiPS concentration, enabled by greater solubility, suppresses ηcon and thereby accelerates LiPS reduction (Figure 4c).53 Notably, the DOL/F4DEE electrolyte with moderate LiPS solubility dissolves sufficient LiPS to sustain favorable sulfur cathode kinetics, as discussed in the following section. ■EXTENDED LI−S CYCLE LIFE USING THE DOL/F4DEE ELECTROLYTE The benefits of the DOL/F4DEE electrolyte on Li−S electrochemical performance were evaluated in Li−S batteries with optimized LiNO3 additive concentration (Figure S28).</t>
+          <t>For example, at 70% depth of discharge (DOD) (a typical state of the liquid−solid conversion) in Li||CP GITT with DOL/DME catholytes, ηcon increased from 177.7 mV at 0.4 M Li2S6 to 246.7 mV at Figure 4.</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>LiPS 溶解度 → 抑制 ηcon → 动力学；F4DEE 中等溶解度够用；后半是小标题和下一段开头</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>✅ S39-M32</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>✅ S39-M8</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>✅ S39-M16</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>✅ S39-M4</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
+          <t>纯数据：ηcon 随 Li₂S₆ 浓度的数值</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>❌错提 S39-M11</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>M0137</t>
+          <t>M0136</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3563,7 +3767,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>GITT experiments in Li||C/S cells with practical C/S cathodes further confirmed that the sulfur cathode kinetics is strongly governed by LiPS solubility.</t>
+          <t>These results highlight the critical role of LiPS solubility in governing Li−S redox kinetics: higher LiPS concentration, enabled by greater solubility, suppresses ηcon and thereby accelerates LiPS reduction (Figure 4c).53 Notably, the DOL/F4DEE electrolyte with moderate LiPS solubility dissolves sufficient LiPS to sustain favorable sulfur cathode kinetics, as discussed in the following section. ■EXTENDED LI−S CYCLE LIFE USING THE DOL/F4DEE ELECTROLYTE The benefits of the DOL/F4DEE electrolyte on Li−S electrochemical performance were evaluated in Li−S batteries with optimized LiNO3 additive concentration (Figure S28).</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3573,39 +3777,44 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Li‖C/S GITT 进一步证实正极动力学受 LiPS 溶解度支配</t>
+          <t>LiPS 溶解度 → 抑制 ηcon → 动力学；F4DEE 中等溶解度够用；后半是小标题和下一段开头</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M32</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M8</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M16</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M4</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M11</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>M0139</t>
+          <t>M0137</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3620,7 +3829,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Among the tested electrolytes, DOL/DME delivers the highest discharge capacity (Figure S29), reflecting enhanced liquid−liquid LiPS conversion due to strong LiPS solvation.</t>
+          <t>GITT experiments in Li||C/S cells with practical C/S cathodes further confirmed that the sulfur cathode kinetics is strongly governed by LiPS solubility.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3630,12 +3839,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>DOL/DME 容量最高，归因于强 LiPS 溶剂化促进液–液转化</t>
+          <t>Li‖C/S GITT 进一步证实正极动力学受 LiPS 溶解度支配</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M33</t>
+          <t>❌漏</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3654,6 +3863,11 @@
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
         </is>
@@ -3662,7 +3876,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>M0141</t>
+          <t>M0139</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3677,7 +3891,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Notably, DOL/F4DEE outperforms DOL/TTE in LiPS redox kinetics due to its higher LiPS solubility.</t>
+          <t>Among the tested electrolytes, DOL/DME delivers the highest discharge capacity (Figure S29), reflecting enhanced liquid−liquid LiPS conversion due to strong LiPS solvation.</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3687,12 +3901,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>F4DEE 动力学优于 TTE，归因于溶解度更高</t>
+          <t>DOL/DME 容量最高，归因于强 LiPS 溶剂化促进液–液转化</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M34</t>
+          <t>✅ S39-M33</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3707,19 +3921,24 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M4</t>
+          <t>❌漏</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M3</t>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>M0142</t>
+          <t>M0141</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3734,33 +3953,54 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Furthermore, deconvolution of the GITT overpotential confirmed that concentration polarization dominates the overall redox kinetics (Figure S31).</t>
+          <t>Notably, DOL/F4DEE outperforms DOL/TTE in LiPS redox kinetics due to its higher LiPS solubility.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>过电位分解结果（浓差极化占主导），同 M0126，没连到电解液性质</t>
+          <t>F4DEE 动力学优于 TTE，归因于溶解度更高</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>❌错提 S39-M35</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="inlineStr"/>
+          <t>✅ S39-M34</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M4</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M3</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>M0143</t>
+          <t>M0142</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3775,49 +4015,34 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Taken together, these Li||C/S GITT results, consistent with the earlier Li||CP experiments using varied Li2S6 concentrations, underscore the advantage of moderate LiPS solubility in DOL/F4DEE for enhancing sulfur cathode kinetics.</t>
+          <t>Furthermore, deconvolution of the GITT overpotential confirmed that concentration polarization dominates the overall redox kinetics (Figure S31).</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>小结：中等 LiPS 溶解度有利于正极动力学</t>
+          <t>过电位分解结果（浓差极化占主导），同 M0126，没连到电解液性质</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>✅ S39-M4</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>❌错提 S39-M35</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>M0146</t>
+          <t>M0143</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3832,7 +4057,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>The DOL/F4DEE cell, similar to the DOL/DME one, typically exhibits two well-defined plateaus, indicating sufficient sulfur utilization owing to its moderate LiPS solubility.</t>
+          <t>Taken together, these Li||C/S GITT results, consistent with the earlier Li||CP experiments using varied Li2S6 concentrations, underscore the advantage of moderate LiPS solubility in DOL/F4DEE for enhancing sulfur cathode kinetics.</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3842,12 +4067,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>中等溶解度 → 两个平台完整 → 硫利用充分</t>
+          <t>小结：中等 LiPS 溶解度有利于正极动力学</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M36</t>
+          <t>❌漏</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3862,10 +4087,15 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M4</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
         </is>
@@ -3874,7 +4104,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>M0147</t>
+          <t>M0146</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3889,7 +4119,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>On the contrary, DOL/TTE with poor LiPS solubility results in a depressed second discharge plateau with reduced specific capacity.</t>
+          <t>The DOL/F4DEE cell, similar to the DOL/DME one, typically exhibits two well-defined plateaus, indicating sufficient sulfur utilization owing to its moderate LiPS solubility.</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3899,17 +4129,17 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>TTE 溶解度低 → 第二平台压低、容量低</t>
+          <t>中等溶解度 → 两个平台完整 → 硫利用充分</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M37</t>
+          <t>✅ S39-M36</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M9</t>
+          <t>❌漏</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3919,10 +4149,15 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M6</t>
+          <t>❌漏</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
         </is>
@@ -3931,7 +4166,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>M0149</t>
+          <t>M0147</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3946,7 +4181,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Strong Li+ solvation and strong LiPS solvation in DOL/DME trigger poor sulfur reversibility and severe Li anode degradation, resulting in quick capacity fading after only 55 cycles.</t>
+          <t>On the contrary, DOL/TTE with poor LiPS solubility results in a depressed second discharge plateau with reduced specific capacity.</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3956,39 +4191,44 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>强 Li⁺、强 LiPS 溶剂化 → 可逆性差、负极退化 → 55 圈后快速衰减（强侧核心句）</t>
+          <t>TTE 溶解度低 → 第二平台压低、容量低</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M38</t>
+          <t>✅ S39-M37</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M10</t>
+          <t>✅ S39-M9</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M17</t>
+          <t>❌漏</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M5</t>
+          <t>✅ S39-M6</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M4</t>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>M0150</t>
+          <t>M0149</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -4003,7 +4243,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>This corresponds to the decoupled impacts of longchain LiPS corrosion and low CE due to the poor Li SEI.</t>
+          <t>Strong Li+ solvation and strong LiPS solvation in DOL/DME trigger poor sulfur reversibility and severe Li anode degradation, resulting in quick capacity fading after only 55 cycles.</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -4013,17 +4253,17 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>接上句：长链 LiPS 腐蚀 + SEI 差导致 CE 低</t>
+          <t>强 Li⁺、强 LiPS 溶剂化 → 可逆性差、负极退化 → 55 圈后快速衰减（强侧核心句）</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M39</t>
+          <t>✅ S39-M38</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M10</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -4039,18 +4279,23 @@
       <c r="K59" s="2" t="inlineStr">
         <is>
           <t>✅ S39-M4</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M12</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>M0157</t>
+          <t>M0150</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>正文 p8</t>
+          <t>正文 p7</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4060,7 +4305,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>DOL/TTE continuously suffers from poor sulfur active material utilization due to low LiPS solubility, as revealed from its slow capacity activation and overpotential recovery (Figure S33).</t>
+          <t>This corresponds to the decoupled impacts of longchain LiPS corrosion and low CE due to the poor Li SEI.</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -4070,12 +4315,12 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>TTE 溶解度低 → 硫利用差</t>
+          <t>接上句：长链 LiPS 腐蚀 + SEI 差导致 CE 低</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M40</t>
+          <t>✅ S39-M39</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4085,24 +4330,29 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M18</t>
+          <t>✅ S39-M17</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M6</t>
+          <t>✅ S39-M5</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M4</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M12</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>M0158</t>
+          <t>M0157</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -4117,7 +4367,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>DOL/F4DEE stabilizes the Li anode with moderate Li+ solvation and weak LiPS solvation, while maintaining sufficient cathode kinetics owing to its moderate LiPS solubility.</t>
+          <t>DOL/TTE continuously suffers from poor sulfur active material utilization due to low LiPS solubility, as revealed from its slow capacity activation and overpotential recovery (Figure S33).</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -4127,39 +4377,44 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>小结：F4DEE 两侧兼顾的原因</t>
+          <t>TTE 溶解度低 → 硫利用差</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M41</t>
+          <t>✅ S39-M40</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M11</t>
+          <t>❌漏</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M19</t>
+          <t>✅ S39-M18</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M6</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M13</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>M0159</t>
+          <t>M0158</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4174,7 +4429,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>These attributes contribute to a highly prolonged Li−S cycle life of over 180 cycles.</t>
+          <t>DOL/F4DEE stabilizes the Li anode with moderate Li+ solvation and weak LiPS solvation, while maintaining sufficient cathode kinetics owing to its moderate LiPS solubility.</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -4184,17 +4439,17 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>接上句：这些性质 → 寿命 180 圈以上</t>
+          <t>小结：F4DEE 两侧兼顾的原因</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M41</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M11</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -4210,13 +4465,18 @@
       <c r="K62" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>❌漏（挂在设计主张）</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>M0161</t>
+          <t>M0159</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -4231,7 +4491,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>DOL/F4DEE and DOL/DME facilitate sulfur redox kinetics owing to LiPS solubility advantages, reflected by a smaller charge transfer resistance (Rct).</t>
+          <t>These attributes contribute to a highly prolonged Li−S cycle life of over 180 cycles.</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -4241,12 +4501,12 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>EIS：溶解度优势 → Rct 小 → 动力学快</t>
+          <t>接上句：这些性质 → 寿命 180 圈以上</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M42</t>
+          <t>❌漏</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4256,7 +4516,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M19</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -4265,6 +4525,11 @@
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
         </is>
@@ -4273,7 +4538,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>M0162</t>
+          <t>M0161</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4288,7 +4553,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>On the other hand, the smaller SEI resistance (RSEI) in DOL/F4DEE and DOL/TTE than DOL/DME indicates the benefit of weakened Li+ and LiPS solvation on Li anode.</t>
+          <t>DOL/F4DEE and DOL/DME facilitate sulfur redox kinetics owing to LiPS solubility advantages, reflected by a smaller charge transfer resistance (Rct).</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -4298,12 +4563,12 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>EIS：溶剂化弱 → RSEI 小 → 有利负极</t>
+          <t>EIS：溶解度优势 → Rct 小 → 动力学快</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M43</t>
+          <t>✅ S39-M42</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4322,6 +4587,11 @@
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
         </is>
@@ -4330,7 +4600,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>M0163</t>
+          <t>M0162</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4345,27 +4615,27 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>The drastic increase of Rbulk in DOL/DME (which may come from electrolyte dry-out9) further proves its poor Li cyclability.</t>
+          <t>On the other hand, the smaller SEI resistance (RSEI) in DOL/F4DEE and DOL/TTE than DOL/DME indicates the benefit of weakened Li+ and LiPS solvation on Li anode.</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Rbulk 增大“may come from electrolyte dry-out”：推测（电解液消耗）</t>
+          <t>EIS：溶剂化弱 → RSEI 小 → 有利负极</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M44</t>
+          <t>✅ S39-M43</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M15</t>
+          <t>❌漏</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -4375,10 +4645,15 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>✅⚠️标“本文结论” S39-M11</t>
+          <t>❌漏</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
         </is>
@@ -4387,7 +4662,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>M0167</t>
+          <t>M0163</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4397,34 +4672,59 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>结论</t>
+          <t>正文</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>The DOL/F4DEE electrolyte, with moderate Li+ solvation, promotes the formation of a fluorine-rich SEI layer, effectively regulating lithium stripping and plating.</t>
+          <t>The drastic increase of Rbulk in DOL/DME (which may come from electrolyte dry-out9) further proves its poor Li cyclability.</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>结论：中等 Li⁺ 溶剂化 → 富氟 SEI → 调控沉积/剥离；正文对应句 M0072、M0077</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="inlineStr"/>
+          <t>Rbulk 增大“may come from electrolyte dry-out”：推测（电解液消耗）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M44</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M15</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>✅⚠️标“本文结论” S39-M11</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M14</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>M0168</t>
+          <t>M0167</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4439,7 +4739,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Its weak LiPS solvation suppresses the formation of corrosive long-chain polysulfides, contributing to an improved anode stability and enhanced sulfur cathode reversibility.</t>
+          <t>The DOL/F4DEE electrolyte, with moderate Li+ solvation, promotes the formation of a fluorine-rich SEI layer, effectively regulating lithium stripping and plating.</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -4449,7 +4749,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>结论：弱 LiPS 溶剂化 → 抑制长链 LiPS → 负极稳定、正极可逆；正文对应句 M0118</t>
+          <t>结论：中等 Li⁺ 溶剂化 → 富氟 SEI → 调控沉积/剥离；正文对应句 M0072、M0077</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
@@ -4457,11 +4757,12 @@
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>M0169</t>
+          <t>M0168</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4476,7 +4777,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Additionally, the electrolyte’s moderate LiPS solubility minimizes concentration polarization, enabling favorable sulfur redox kinetics.</t>
+          <t>Its weak LiPS solvation suppresses the formation of corrosive long-chain polysulfides, contributing to an improved anode stability and enhanced sulfur cathode reversibility.</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -4486,7 +4787,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>结论：中等 LiPS 溶解度 → 浓差极化小 → 动力学好；正文对应句 M0136</t>
+          <t>结论：弱 LiPS 溶剂化 → 抑制长链 LiPS → 负极稳定、正极可逆；正文对应句 M0118</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
@@ -4494,11 +4795,12 @@
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>M0170</t>
+          <t>M0169</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4513,7 +4815,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>These combined features lead to an extended cycle life for Li−S batteries.</t>
+          <t>Additionally, the electrolyte’s moderate LiPS solubility minimizes concentration polarization, enabling favorable sulfur redox kinetics.</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -4523,7 +4825,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>结论：以上 → 寿命延长；正文对应句 M0158、M0159</t>
+          <t>结论：中等 LiPS 溶解度 → 浓差极化小 → 动力学好；正文对应句 M0136</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr"/>
@@ -4531,52 +4833,50 @@
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>S0093</t>
+          <t>M0170</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SI p11</t>
+          <t>正文 p8</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>SI Note S1</t>
+          <t>结论</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Note S1 The PFG structure of F4DEE determines its high LiTFSI solubility but moderate Li+ solvation LiTFSI solubility increases in solvents that either disperse LiTFSI more effectively or interact with Li+ more strongly.</t>
+          <t>These combined features lead to an extended cycle life for Li−S batteries.</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Note S1 标题 + 盐溶解度的通用规律：性质来源</t>
+          <t>结论：以上 → 寿命延长；正文对应句 M0158、M0159</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>🔶应放性质 S39-M7</t>
-        </is>
-      </c>
+      <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>S0095</t>
+          <t>S0093</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4591,7 +4891,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Compared to DME, the extra fluorine atoms in F4DEE show strong electron withdrawing effect, dispersing the electron density on oxygen coordination centers.</t>
+          <t>Note S1 The PFG structure of F4DEE determines its high LiTFSI solubility but moderate Li+ solvation LiTFSI solubility increases in solvents that either disperse LiTFSI more effectively or interact with Li+ more strongly.</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4601,7 +4901,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>性质来源：氟的吸电子效应</t>
+          <t>Note S1 标题 + 盐溶解度的通用规律：性质来源</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr"/>
@@ -4613,11 +4913,12 @@
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>S0096</t>
+          <t>S0095</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4632,7 +4933,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Therefore, F4DEE shows lower electron donicity, resulting in weaker Li+ solvating power than DME.</t>
+          <t>Compared to DME, the extra fluorine atoms in F4DEE show strong electron withdrawing effect, dispersing the electron density on oxygen coordination centers.</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4642,7 +4943,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>性质来源：给电子能力低 → Li⁺ 溶剂化弱</t>
+          <t>性质来源：氟的吸电子效应</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
@@ -4654,11 +4955,12 @@
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>S0100</t>
+          <t>S0096</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4673,7 +4975,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Meanwhile, the electron withdrawing effect of fluorine on -CF2H terminal groups increases the local polarity of F4DEE,7 resulting in increased LiTFSI solubility (Figure S9b).</t>
+          <t>Therefore, F4DEE shows lower electron donicity, resulting in weaker Li+ solvating power than DME.</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -4683,7 +4985,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>性质来源：局部极性 → 盐溶解度（带引文 7）</t>
+          <t>性质来源：给电子能力低 → Li⁺ 溶剂化弱</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr"/>
@@ -4695,11 +4997,12 @@
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>S0101</t>
+          <t>S0100</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4714,7 +5017,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>In all, the PFG structure endows F4DEE with high electronic polarizability but low electron donicity, resulting in high LiTFSI solubility but moderate Li+ solvation in F4DEE.</t>
+          <t>Meanwhile, the electron withdrawing effect of fluorine on -CF2H terminal groups increases the local polarity of F4DEE,7 resulting in increased LiTFSI solubility (Figure S9b).</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4724,7 +5027,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>性质来源小结</t>
+          <t>性质来源：局部极性 → 盐溶解度（带引文 7）</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr"/>
@@ -4736,68 +5039,54 @@
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>S0119</t>
+          <t>S0101</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SI p13</t>
+          <t>SI p11</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>SI Note S2</t>
+          <t>SI Note S1</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Despite these disparities, all electrolytes in our study possess high Li+ conductivity of &gt; 1.0 mS cm-1, already ensuring fast Li+ transport.</t>
+          <t>In all, the PFG structure endows F4DEE with high electronic polarizability but low electron donicity, resulting in high LiTFSI solubility but moderate Li+ solvation in F4DEE.</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>排除性说法：所有电解液电导率都 &gt; 1 mS/cm，传输都够快</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>性质来源小结</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M8</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>🔶应放性质 S39-M7</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>S0120</t>
+          <t>S0119</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4812,7 +5101,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Thus, the impact of Li+ conductivity in our study is relatively small, which will be further discussed in Note S3.</t>
+          <t>Despite these disparities, all electrolytes in our study possess high Li+ conductivity of &gt; 1.0 mS cm-1, already ensuring fast Li+ transport.</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4822,7 +5111,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>排除性说法：电导率的影响相对小</t>
+          <t>排除性说法：所有电解液电导率都 &gt; 1 mS/cm，传输都够快</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -4842,10 +5131,15 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M8</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
         </is>
@@ -4854,22 +5148,22 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>S0154</t>
+          <t>S0120</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SI p20</t>
+          <t>SI p13</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>SI Note S3</t>
+          <t>SI Note S2</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>All electrolytes exhibit Li+ conductivity above 1 mS cm-1 (see Note S2), which is sufficient to support facile Li+ transport.</t>
+          <t>Thus, the impact of Li+ conductivity in our study is relatively small, which will be further discussed in Note S3.</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4879,7 +5173,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>排除性说法（与 S0119 重复）</t>
+          <t>排除性说法：电导率的影响相对小</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -4899,10 +5193,15 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M8</t>
+          <t>❌漏</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
         </is>
@@ -4911,7 +5210,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>S0155</t>
+          <t>S0154</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4926,7 +5225,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Notably, the DOL/DME electrolyte, despite its superior Li+ conductivity, shows poorer Li anode cyclability than DOL/F4DEE.</t>
+          <t>All electrolytes exhibit Li+ conductivity above 1 mS cm-1 (see Note S2), which is sufficient to support facile Li+ transport.</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4936,12 +5235,12 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>DOL/DME 电导率最高但负极最差</t>
+          <t>排除性说法（与 S0119 重复）</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M13</t>
+          <t>❌漏</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4962,13 +5261,18 @@
       <c r="K78" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M6</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>S0156</t>
+          <t>S0155</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4983,7 +5287,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>This indicates that the bulk conductivity is not the primary reason for the observed Li stability differences.</t>
+          <t>Notably, the DOL/DME electrolyte, despite its superior Li+ conductivity, shows poorer Li anode cyclability than DOL/F4DEE.</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4993,7 +5297,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>接上句：体相电导率不是负极差异的主因（排除性）</t>
+          <t>DOL/DME 电导率最高但负极最差</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -5003,7 +5307,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M13</t>
+          <t>❌漏</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -5019,13 +5323,18 @@
       <c r="K79" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>S0157</t>
+          <t>S0156</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -5040,33 +5349,54 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>(2) Interfacial charge transfer kinetics.</t>
+          <t>This indicates that the bulk conductivity is not the primary reason for the observed Li stability differences.</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>小标题“(2) Interfacial charge transfer kinetics.”</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr"/>
+          <t>接上句：体相电导率不是负极差异的主因（排除性）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M13</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M13</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>❌错提 S39-M9</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr"/>
+          <t>✅ S39-M8</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M6</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>S0158</t>
+          <t>S0157</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -5081,7 +5411,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>We assessed the Li|electrolyte interfacial kinetics using Li||Cu stripping/plating experiments.</t>
+          <t>(2) Interfacial charge transfer kinetics.</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -5091,7 +5421,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>方法</t>
+          <t>小标题“(2) Interfacial charge transfer kinetics.”</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr"/>
@@ -5103,11 +5433,12 @@
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>S0159</t>
+          <t>S0158</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -5122,7 +5453,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Figure S17 summarizes the voltage profiles with the DOL/DME, DOL/F4DEE, and DOL/TTE electrolytes, obtained via the Li||Cu Aurbach method.</t>
+          <t>We assessed the Li|electrolyte interfacial kinetics using Li||Cu stripping/plating experiments.</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -5132,7 +5463,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>图的描述</t>
+          <t>方法</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr"/>
@@ -5144,11 +5475,12 @@
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>S0161</t>
+          <t>S0159</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -5163,7 +5495,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Therefore, the observed overpotential is attributed to the Li|electrolyte interfacial processes.</t>
+          <t>Figure S17 summarizes the voltage profiles with the DOL/DME, DOL/F4DEE, and DOL/TTE electrolytes, obtained via the Li||Cu Aurbach method.</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -5173,7 +5505,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>方法上的归属（过电位来自界面过程），不涉及电解液性质</t>
+          <t>图的描述</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr"/>
@@ -5185,11 +5517,12 @@
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>S0162</t>
+          <t>S0160</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5204,49 +5537,34 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>All three electrolytes exhibit similarly low overpotentials (less than 20 mV), indicating that the impact of interfacial kinetics is negligible during lithium stripping/plating.</t>
+          <t>During the ten highlighted stripping/plating cycles (1 mAh cm-2, 0.5 mA cm-2), a lithium reservoir consistently remains on the Cu electrode.</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>排除性说法：三种电解液过电位都低，界面动力学影响可忽略</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>✅ S39-M14</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>✅ S39-M9</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
+          <t>实验观察：Cu 上始终留有锂库，没有机制</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>❌错提 S39-M7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>S0164</t>
+          <t>S0161</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -5261,49 +5579,38 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>LiF is well known to regulate Li deposition because of its electrochemical stability and mechanical strength.</t>
+          <t>Therefore, the observed overpotential is attributed to the Li|electrolyte interfacial processes.</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>“LiF is well known to regulate Li deposition”：SI 里的通用说法，支撑本文 SEI 解释，照记、标转述</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>方法上的归属（过电位来自界面过程），不涉及电解液性质</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
+          <t>❌错提 S39-M9</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>❌错提 S39-M7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>S0165</t>
+          <t>S0162</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5318,7 +5625,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Therefore, the LiF-rich SEI layer formed by the DOL/F4DEE electrolyte effectively suppresses Li dendrite growth, leading to enhanced Li cyclability.7, 9 Figure S17.</t>
+          <t>All three electrolytes exhibit similarly low overpotentials (less than 20 mV), indicating that the impact of interfacial kinetics is negligible during lithium stripping/plating.</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -5328,12 +5635,12 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>富 LiF SEI → 抑制枝晶 → 锂循环好（引文 7、9，与他文一致）</t>
+          <t>排除性说法：三种电解液过电位都低，界面动力学影响可忽略</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M14</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5348,34 +5655,39 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M9</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>S0169</t>
+          <t>S0164</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SI p21</t>
+          <t>SI p20</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>SI Note S4</t>
+          <t>SI Note S3</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>SI-20 Note S4 Suppressed lithium anode chemical corrosion with weak LiPS solvation LiPS in Li-S batteries, especially long-chain species (x = 5 ~ 8 in Li2Sx), can chemically corrode Li anode, causing irreversible Li inventory loss.10, 11 Here we quantified the effect of LiPS solvation on this parasitic reaction via titration gas chromatography (TGC).</t>
+          <t>LiF is well known to regulate Li deposition because of its electrochemical stability and mechanical strength.</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -5385,7 +5697,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Note S4 标题 + 背景（长链 LiPS 腐蚀锂，引文 10、11）+ 方法；不在引言，按 10-25 口径照记、标转述</t>
+          <t>“LiF is well known to regulate Li deposition”：SI 里的通用说法，支撑本文 SEI 解释，照记、标转述</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -5405,10 +5717,15 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>✅⚠️标“本文结论” S39-M10</t>
+          <t>❌漏</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
         </is>
@@ -5417,48 +5734,69 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>S0170</t>
+          <t>S0165</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>SI p21</t>
+          <t>SI p20</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>SI Note S4</t>
+          <t>SI Note S3</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Li metal chips were soaked in 1.0 mL LiPS solutions (0.1 M Li2S6 dissolved in DOL/DME, DOL/F4DEE or DOL/TTE) for 25 days.</t>
+          <t>Therefore, the LiF-rich SEI layer formed by the DOL/F4DEE electrolyte effectively suppresses Li dendrite growth, leading to enhanced Li cyclability.7, 9 Figure S17.</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>实验步骤</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr"/>
+          <t>富 LiF SEI → 抑制枝晶 → 锂循环好（引文 7、9，与他文一致）</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>❌错提 S39-M10</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr"/>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>S0177</t>
+          <t>S0169</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5473,22 +5811,22 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>S2) Per Figure S18b, LiPS solutions with weaker LiPS solvation result in lower Li inventory loss ratio.</t>
+          <t>SI-20 Note S4 Suppressed lithium anode chemical corrosion with weak LiPS solvation LiPS in Li-S batteries, especially long-chain species (x = 5 ~ 8 in Li2Sx), can chemically corrode Li anode, causing irreversible Li inventory loss.10, 11 Here we quantified the effect of LiPS solvation on this parasitic reaction via titration gas chromatography (TGC).</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>LiPS 溶剂化越弱，锂库存损失越少</t>
+          <t>Note S4 标题 + 背景（长链 LiPS 腐蚀锂，引文 10、11）+ 方法；不在引言，按 10-25 口径照记、标转述</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M12</t>
+          <t>❌漏</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5498,15 +5836,20 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M20</t>
+          <t>❌漏</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M10</t>
+          <t>✅⚠️标“本文结论” S39-M10</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
         </is>
@@ -5515,7 +5858,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>S0178</t>
+          <t>S0170</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5530,64 +5873,49 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>This proves that weak LiPS solvation can suppress chemical corrosion on Li anode despite its relatively small benefit.</t>
+          <t>Li metal chips were soaked in 1.0 mL LiPS solutions (0.1 M Li2S6 dissolved in DOL/DME, DOL/F4DEE or DOL/TTE) for 25 days.</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>接上句：弱 LiPS 溶剂化能抑制锂腐蚀（作者说益处较小）</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>✅ S39-M12</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>✅ S39-M14</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>✅ S39-M20</t>
-        </is>
-      </c>
+          <t>实验步骤</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M10</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
+          <t>❌错提 S39-M10</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>S0212</t>
+          <t>S0177</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>SI p23</t>
+          <t>SI p21</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>SI Note S5</t>
+          <t>SI Note S4</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>The overpotential on each stage does not significantly change with varied LiPS solvation, again evidencing the non-correlation between LiPS solvation and LiPS reduction kinetics.</t>
+          <t>S2) Per Figure S18b, LiPS solutions with weaker LiPS solvation result in lower Li inventory loss ratio.</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -5597,12 +5925,12 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>各段过电位不随 LiPS 溶剂化变 → 溶剂化与还原动力学无关（排除性）</t>
+          <t>LiPS 溶剂化越弱，锂库存损失越少</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M12</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5612,39 +5940,44 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M20</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M10</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>S0213</t>
+          <t>S0178</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>SI p23</t>
+          <t>SI p21</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>SI Note S5</t>
+          <t>SI Note S4</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>(3) The discharge capacity on stage II maintains the same order of DOL/DME &gt; DOL/F4DEE &gt; DOL/TTE, demonstrating the favored liquid-liquid LiPS reduction with strong LiPS solvation.</t>
+          <t>This proves that weak LiPS solvation can suppress chemical corrosion on Li anode despite its relatively small benefit.</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -5654,121 +5987,168 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>第 II 段容量顺序 → 强 LiPS 溶剂化利于液–液还原</t>
+          <t>接上句：弱 LiPS 溶剂化能抑制锂腐蚀（作者说益处较小）</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>✅ S39-M47</t>
+          <t>✅ S39-M12</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M14</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M20</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>❌漏</t>
+          <t>✅ S39-M10</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
           <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>S0225</t>
+          <t>S0212</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SI p26</t>
+          <t>SI p23</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SI Note S5</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>S5 and completely dissolves in the electrolyte, the maximum Li2S6 concentration is 0.52 M. 3 S8 (s) + 8 Li+ + 8 e- → 4 Li2S6 (sol) (Eq.</t>
+          <t>The overpotential on each stage does not significantly change with varied LiPS solvation, again evidencing the non-correlation between LiPS solvation and LiPS reduction kinetics.</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>计算 Li₂S₆ 最大浓度</t>
+          <t>各段过电位不随 LiPS 溶剂化变 → 溶剂化与还原动力学无关（排除性）</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>❌错提 S39-M45</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr"/>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-      <c r="K93" s="2" t="inlineStr"/>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>S0226</t>
+          <t>S0213</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>SI p26</t>
+          <t>SI p23</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SI Note S5</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>S5) This value is lower than Li2S6 solubility in DOL/DME but exceeds that in DOL/F4DEE and DOL/TTE.</t>
+          <t>(3) The discharge capacity on stage II maintains the same order of DOL/DME &gt; DOL/F4DEE &gt; DOL/TTE, demonstrating the favored liquid-liquid LiPS reduction with strong LiPS solvation.</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>数值比较（接 S0225）</t>
+          <t>第 II 段容量顺序 → 强 LiPS 溶剂化利于液–液还原</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>❌错提 S39-M45</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-      <c r="K94" s="2" t="inlineStr"/>
+          <t>✅ S39-M47</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>S0227</t>
+          <t>S0225</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5783,83 +6163,181 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>This indicates that the moderate LiPS solubility in DOL/F4DEE electrolyte limits the soluble LiPS concentration.</t>
+          <t>S5 and completely dissolves in the electrolyte, the maximum Li2S6 concentration is 0.52 M. 3 S8 (s) + 8 Li+ + 8 e- → 4 Li2S6 (sol) (Eq.</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>只讲性质本身：中等溶解度限制可溶 LiPS 浓度，没有落到过程</t>
+          <t>计算 Li₂S₆ 最大浓度</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>🔶应放性质 S39-M45</t>
+          <t>❌错提 S39-M45</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>S0226</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>SI p26</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>S5) This value is lower than Li2S6 solubility in DOL/DME but exceeds that in DOL/F4DEE and DOL/TTE.</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>数值比较（接 S0225）</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>❌错提 S39-M45</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>❌错提 S39-M15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>S0227</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>SI p26</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>This indicates that the moderate LiPS solubility in DOL/F4DEE electrolyte limits the soluble LiPS concentration.</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>只讲性质本身：中等溶解度限制可溶 LiPS 浓度，没有落到过程</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>🔶应放性质 S39-M45</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>🔶应放性质 S39-M15</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
           <t>S0265</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>SI p37</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>SI 图注</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Li-S cell with DOL/TTE experiences a slow capacity activation and overpotential recovery process, demonstrating the negative effects of its poor LiPS solubility.</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>TTE 容量活化慢、过电位恢复慢 → 溶解度低的负面作用</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>✅ S39-M12</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
         <is>
           <t>✅ S39-M6</t>
         </is>
       </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>❌漏</t>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>✅ S39-M13</t>
         </is>
       </c>
     </row>
@@ -5874,7 +6352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6038,7 +6516,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>五家都没挂的应记句</t>
+          <t>各家都没挂的应记句</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -6167,6 +6645,29 @@
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>错提</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>智谱GLM-5.3关思考 挂了不该记的句子</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>引言背景、纯数据/方法/小标题/计算</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>M0071、M0127、S0160、S0161、S0226</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/云端_2026-10-25_千问调试集53篇/S39_机制句复核/S39_机制句复核.xlsx
+++ b/output/云端_2026-10-25_千问调试集53篇/S39_机制句复核/S39_机制句复核.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐句复核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题汇总" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="召回率与精确率" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐句复核" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题汇总" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1020,6 +1021,372 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>机制句召回</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>机制句精确率</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>梯度召回</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>梯度精确率</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>测试召回</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>测试精确率</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>配方数</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>结果条数（对错未判）</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>77%（43/56）</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>100%（5/5）</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>100%（10/10）</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Claude 子代理，对话内提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>29%（16/56）</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>60%（3/5）</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>100%（10/10）</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>GPT 子代理，对话内提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>千问Max关思考</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>41%（23/56）</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40%（2/5）</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>70%（7/10）</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>格式 3 轮未过；程序删一个多余括号后仅供对比，未冻结</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>千问27B开思考</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>48%（27/56）</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20%（1/5）</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>70%（7/10）</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>千问27B关思考</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>20%（11/56）</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20%（1/5）</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>40%（4/10）</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>智谱GLM-5.3关思考</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>39%（22/56）</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>20%（1/5）</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>60%（6/10）</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>API；用新版提示词 v2（含 10-25 机制句口径），其余各家用旧版</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6346,7 +6713,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/output/云端_2026-10-25_千问调试集53篇/S39_机制句复核/S39_机制句复核.xlsx
+++ b/output/云端_2026-10-25_千问调试集53篇/S39_机制句复核/S39_机制句复核.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="召回率与精确率" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐句复核" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题汇总" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="按说法" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="召回率与精确率" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐句复核" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题汇总" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1021,358 +1022,749 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>模型</t>
+          <t>说法编号</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>机制句召回</t>
+          <t>作者的说法（AI 概括）</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>机制句精确率</t>
+          <t>归入的原句</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>梯度召回</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>梯度精确率</t>
+          <t>GPT</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>测试召回</t>
+          <t>千问Max关思考</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>测试精确率</t>
+          <t>千问27B开思考</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>配方数</t>
+          <t>千问27B关思考</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>结果条数（对错未判）</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>说明</t>
+          <t>智谱GLM-5.3关思考</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Claude</t>
+          <t>C01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>77%（43/56）</t>
+          <t>中等 Li⁺ 溶剂化（溶剂化层富 TFSI⁻/F4DEE）→ 富 LiF SEI → 锂沉积致密 → CE 高、负极稳定</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>M0069、M0070、M0072、M0073、M0077、M0078、M0087、M0162、S0164、S0165、M0003、M0022、M0167</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>100%（5/5）</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>100%（10/10）</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Claude 子代理，对话内提取</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>C02</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>29%（16/56）</t>
+          <t>弱 LiPS 溶剂化 / 适中溶解度 → 腐蚀性长链 LiPS 少 → 锂负极化学腐蚀少</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>M0078、M0086、S0169、S0177、S0178、M0024、M0168</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>60%（3/5）</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>100%（10/10）</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>GPT 子代理，对话内提取</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>千问Max关思考</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>41%（23/56）</t>
+          <t>LiPS 溶剂化影响转化热力学而不影响动力学：各电解液过电位相近，容量差来自热力学（与“弱溶剂化动力学差”的传统看法不同）</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>M0100、M0101、M0102、M0108、S0212、M0004</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>40%（2/5）</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>❌漏</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70%（7/10）</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>格式 3 轮未过；程序删一个多余括号后仅供对比，未冻结</t>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>千问27B开思考</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>48%（27/56）</t>
+          <t>弱 LiPS 溶剂化 → 液–液还原和固–液氧化受限、更依赖液–固路径 → 容量较低；强溶剂化利于液–液转化</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>M0096、M0097、M0109、M0117、M0139、S0213、M0023</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20%（1/5）</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70%（7/10）</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>API</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>千问27B关思考</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>20%（11/56）</t>
+          <t>强 LiPS 溶剂化 → 液–固氧化不利 → 长链 LiPS 残留 → 下圈容量损失、穿梭腐蚀负极、LiNO₃ 消耗</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>M0111、M0112、M0113、M0114、M0115</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20%（1/5）</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40%（4/10）</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>API</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>智谱GLM-5.3关思考</t>
+          <t>C06</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>39%（22/56）</t>
+          <t>弱 LiPS 溶剂化带来容量–寿命权衡：容量部分损失，但抑制长链 LiPS、可逆性好 → 寿命更长</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>M0115、M0116、M0118、M0097</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20%（1/5）</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60%（6/10）</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>API；用新版提示词 v2（含 10-25 机制句口径），其余各家用旧版</t>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>C07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>LiPS 溶解度 → 可溶 LiPS 浓度 → 浓差极化 → 正极动力学；中等溶解度（F4DEE）够用，太低（TTE）则硫利用差</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>M0119、M0121、M0122、M0136、M0137、M0141、M0143、M0146、M0147、M0157、M0161、S0265、M0025、M0026、M0169</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>C08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>排除性：电导率、界面动力学、Li⁺/负极对整体动力学都不是差异的主因</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>M0021、M0088、S0119、S0120、S0154、S0155、S0156、S0162</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>C09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>强 Li⁺ + 强 LiPS 溶剂化（DOL/DME）→ 硫可逆性差、负极退化（长链 LiPS 腐蚀 + SEI 差导致 CE 低）→ 55 圈后快速衰减</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>M0149、M0150</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>F4DEE 综合：中等 Li⁺ 溶剂化 + 弱 LiPS 溶剂化稳负极，中等溶解度保正极动力学 → 寿命 &gt;180 圈</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>M0158、M0159、M0005、M0170</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>DOL/DME 体相电阻大增，可能来自电解液干涸（推测）→ 锂循环差</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>M0163</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>盐浓度影响 Li⁺ 传输、SEI 和 LiPS 溶解（转述通用规律，用来定 1.0 M LiTFSI）</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>M0067</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>❌漏</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>说法召回</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>100%（12/12）</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>83%（10/12）</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>75%（9/12）</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>75%（9/12）</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>58%（7/12）</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>83%（10/12）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>说法精确率（机制条目里对的）</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>92%（43/47）</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>100%（16/16）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>95%（19/20）</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>91%（10/11）</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%（4/4）</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>93%（14/15）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>错的条目（只挂了引言背景、数据、方法或性质句）</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>S39-M3、S39-M4、S39-M35、S39-M45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>S39-M4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>S39-M7</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>S39-M15</t>
         </is>
       </c>
     </row>
@@ -1382,6 +1774,444 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>机制说法召回</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>机制说法精确率</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>（参考）机制句召回</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>（参考）机制句精确率</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>梯度召回</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>梯度精确率</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>测试召回</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>测试精确率</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>配方数</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>结果条数（对错未判）</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>100%（12/12）</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>77%（43/56）</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>100%（5/5）</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>100%（10/10）</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Claude 子代理，对话内提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>83%（10/12）</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>29%（16/56）</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>60%（3/5）</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>100%（10/10）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>GPT 子代理，对话内提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>千问Max关思考</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>75%（9/12）</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>41%（23/56）</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>40%（2/5）</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>70%（7/10）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>格式 3 轮未过；程序删一个多余括号后仅供对比，未冻结</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>千问27B开思考</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>75%（9/12）</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>48%（27/56）</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20%（1/5）</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>70%（7/10）</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>千问27B关思考</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>58%（7/12）</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20%（11/56）</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20%（1/5）</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>40%（4/10）</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>智谱GLM-5.3关思考</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>83%（10/12）</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>39%（22/56）</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>20%（1/5）</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>60%（6/10）</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>API；用新版提示词 v2（含 10-25 机制句口径），其余各家用旧版</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6713,7 +7543,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
